--- a/research/traditional_assets/database/data/romania/romania_furn_home_furnishings.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_furn_home_furnishings.xlsx
@@ -588,109 +588,115 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.02369186046511628</v>
+        <v>0.01717607973421927</v>
       </c>
       <c r="H2">
-        <v>0.02369186046511628</v>
+        <v>0.01717607973421927</v>
       </c>
       <c r="I2">
-        <v>-0.04665697674418605</v>
+        <v>-0.1093023255813953</v>
       </c>
       <c r="J2">
-        <v>-0.04665697674418605</v>
+        <v>-0.1093023255813953</v>
       </c>
       <c r="K2">
-        <v>-3.12</v>
+        <v>-3.38</v>
       </c>
       <c r="L2">
-        <v>-0.04534883720930233</v>
+        <v>-0.1122923588039867</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.164</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.2171641791044776</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.3443786982248521</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.0007462686567164179</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>-0.001183431952662722</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.16</v>
+      </c>
+      <c r="T2">
+        <v>0.9965635738831615</v>
       </c>
       <c r="U2">
-        <v>0.888</v>
+        <v>0.308</v>
       </c>
       <c r="V2">
-        <v>0.1448613376835237</v>
+        <v>0.05746268656716418</v>
       </c>
       <c r="W2">
-        <v>-0.3</v>
+        <v>-0.2467153284671533</v>
       </c>
       <c r="X2">
-        <v>0.1434103973029761</v>
+        <v>0.2085586261052945</v>
       </c>
       <c r="Y2">
-        <v>-0.4434103973029762</v>
+        <v>-0.4552739545724478</v>
       </c>
       <c r="Z2">
-        <v>4.372974003686519</v>
+        <v>1.606018567922314</v>
       </c>
       <c r="AA2">
-        <v>-0.204029746392932</v>
+        <v>-0.175541564400811</v>
       </c>
       <c r="AB2">
-        <v>0.09027314514304585</v>
+        <v>0.1502201067767823</v>
       </c>
       <c r="AC2">
-        <v>-0.2943028915359779</v>
+        <v>-0.3257616711775933</v>
       </c>
       <c r="AD2">
-        <v>5.93</v>
+        <v>3.84</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>5.93</v>
+        <v>3.84</v>
       </c>
       <c r="AG2">
-        <v>5.042</v>
+        <v>3.532</v>
       </c>
       <c r="AH2">
-        <v>0.4917081260364843</v>
+        <v>0.4173913043478261</v>
       </c>
       <c r="AI2">
-        <v>0.3020886398369842</v>
+        <v>0.3296137339055794</v>
       </c>
       <c r="AJ2">
-        <v>0.4513068385248836</v>
+        <v>0.3972109761583446</v>
       </c>
       <c r="AK2">
-        <v>0.2690214491516381</v>
+        <v>0.3114089225886087</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.355</v>
       </c>
       <c r="AM2">
-        <v>-3.85</v>
+        <v>0.355</v>
       </c>
       <c r="AN2">
-        <v>-121.0204081632653</v>
+        <v>-2.219653179190751</v>
+      </c>
+      <c r="AO2">
+        <v>-9.267605633802818</v>
       </c>
       <c r="AP2">
-        <v>-102.8979591836735</v>
+        <v>-2.041618497109827</v>
       </c>
       <c r="AQ2">
-        <v>0.8337662337662337</v>
+        <v>-9.267605633802818</v>
       </c>
     </row>
     <row r="3">
@@ -710,109 +716,115 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.02369186046511628</v>
+        <v>0.01717607973421927</v>
       </c>
       <c r="H3">
-        <v>0.02369186046511628</v>
+        <v>0.01717607973421927</v>
       </c>
       <c r="I3">
-        <v>-0.04665697674418605</v>
+        <v>-0.1093023255813953</v>
       </c>
       <c r="J3">
-        <v>-0.04665697674418605</v>
+        <v>-0.1093023255813953</v>
       </c>
       <c r="K3">
-        <v>-3.12</v>
+        <v>-3.38</v>
       </c>
       <c r="L3">
-        <v>-0.04534883720930233</v>
+        <v>-0.1122923588039867</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>1.164</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.2171641791044776</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0.3443786982248521</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.004</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.0007462686567164179</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0.001183431952662722</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.16</v>
+      </c>
+      <c r="T3">
+        <v>0.9965635738831615</v>
       </c>
       <c r="U3">
-        <v>0.888</v>
+        <v>0.308</v>
       </c>
       <c r="V3">
-        <v>0.1448613376835237</v>
+        <v>0.05746268656716418</v>
       </c>
       <c r="W3">
-        <v>-0.3</v>
+        <v>-0.2467153284671533</v>
       </c>
       <c r="X3">
-        <v>0.1434103973029761</v>
+        <v>0.2085586261052945</v>
       </c>
       <c r="Y3">
-        <v>-0.4434103973029762</v>
+        <v>-0.4552739545724478</v>
       </c>
       <c r="Z3">
-        <v>4.372974003686519</v>
+        <v>1.606018567922314</v>
       </c>
       <c r="AA3">
-        <v>-0.204029746392932</v>
+        <v>-0.175541564400811</v>
       </c>
       <c r="AB3">
-        <v>0.09027314514304585</v>
+        <v>0.1502201067767823</v>
       </c>
       <c r="AC3">
-        <v>-0.2943028915359779</v>
+        <v>-0.3257616711775933</v>
       </c>
       <c r="AD3">
-        <v>5.93</v>
+        <v>3.84</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5.93</v>
+        <v>3.84</v>
       </c>
       <c r="AG3">
-        <v>5.042</v>
+        <v>3.532</v>
       </c>
       <c r="AH3">
-        <v>0.4917081260364843</v>
+        <v>0.4173913043478261</v>
       </c>
       <c r="AI3">
-        <v>0.3020886398369842</v>
+        <v>0.3296137339055794</v>
       </c>
       <c r="AJ3">
-        <v>0.4513068385248836</v>
+        <v>0.3972109761583446</v>
       </c>
       <c r="AK3">
-        <v>0.2690214491516381</v>
+        <v>0.3114089225886087</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.355</v>
       </c>
       <c r="AM3">
-        <v>-3.85</v>
+        <v>0.355</v>
       </c>
       <c r="AN3">
-        <v>-121.0204081632653</v>
+        <v>-2.219653179190751</v>
+      </c>
+      <c r="AO3">
+        <v>-9.267605633802818</v>
       </c>
       <c r="AP3">
-        <v>-102.8979591836735</v>
+        <v>-2.041618497109827</v>
       </c>
       <c r="AQ3">
-        <v>0.8337662337662337</v>
+        <v>-9.267605633802818</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/romania/romania_furn_home_furnishings.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_furn_home_furnishings.xlsx
@@ -588,115 +588,112 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.01717607973421927</v>
+        <v>-0.2890716803760282</v>
       </c>
       <c r="H2">
-        <v>0.01717607973421927</v>
+        <v>-0.2890716803760282</v>
       </c>
       <c r="I2">
-        <v>-0.1093023255813953</v>
+        <v>-0.4465334900117509</v>
       </c>
       <c r="J2">
-        <v>-0.1093023255813953</v>
+        <v>-0.4465334900117509</v>
       </c>
       <c r="K2">
-        <v>-3.38</v>
+        <v>-3.93</v>
       </c>
       <c r="L2">
-        <v>-0.1122923588039867</v>
+        <v>-0.4618096357226792</v>
       </c>
       <c r="M2">
-        <v>1.164</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.2171641791044776</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.3443786982248521</v>
+        <v>-0</v>
       </c>
       <c r="P2">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.0007462686567164179</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>-0.001183431952662722</v>
+        <v>-0</v>
       </c>
       <c r="S2">
-        <v>1.16</v>
-      </c>
-      <c r="T2">
-        <v>0.9965635738831615</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>0.308</v>
+        <v>0.221</v>
       </c>
       <c r="V2">
-        <v>0.05746268656716418</v>
+        <v>0.06021798365122616</v>
       </c>
       <c r="W2">
-        <v>-0.2467153284671533</v>
+        <v>-0.5032010243277849</v>
       </c>
       <c r="X2">
-        <v>0.2085586261052945</v>
+        <v>0.1773408300189932</v>
       </c>
       <c r="Y2">
-        <v>-0.4552739545724478</v>
+        <v>-0.6805418543467781</v>
       </c>
       <c r="Z2">
-        <v>1.606018567922314</v>
+        <v>0.7503085875506966</v>
       </c>
       <c r="AA2">
-        <v>-0.175541564400811</v>
+        <v>-0.3350379121847999</v>
       </c>
       <c r="AB2">
-        <v>0.1502201067767823</v>
+        <v>0.1182002844005473</v>
       </c>
       <c r="AC2">
-        <v>-0.3257616711775933</v>
+        <v>-0.4532381965853471</v>
       </c>
       <c r="AD2">
-        <v>3.84</v>
+        <v>3.92</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3.84</v>
+        <v>3.92</v>
       </c>
       <c r="AG2">
-        <v>3.532</v>
+        <v>3.699</v>
       </c>
       <c r="AH2">
-        <v>0.4173913043478261</v>
+        <v>0.5164690382081687</v>
       </c>
       <c r="AI2">
-        <v>0.3296137339055794</v>
+        <v>0.2796005706134094</v>
       </c>
       <c r="AJ2">
-        <v>0.3972109761583446</v>
+        <v>0.5019677025376578</v>
       </c>
       <c r="AK2">
-        <v>0.3114089225886087</v>
+        <v>0.2680629031089209</v>
       </c>
       <c r="AL2">
-        <v>0.355</v>
+        <v>0.136</v>
       </c>
       <c r="AM2">
-        <v>0.355</v>
+        <v>0.136</v>
       </c>
       <c r="AN2">
-        <v>-2.219653179190751</v>
+        <v>-1.53125</v>
       </c>
       <c r="AO2">
-        <v>-9.267605633802818</v>
+        <v>-27.94117647058823</v>
       </c>
       <c r="AP2">
-        <v>-2.041618497109827</v>
+        <v>-1.444921875</v>
       </c>
       <c r="AQ2">
-        <v>-9.267605633802818</v>
+        <v>-27.94117647058823</v>
       </c>
     </row>
     <row r="3">
@@ -716,115 +713,112 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.01717607973421927</v>
+        <v>-0.2890716803760282</v>
       </c>
       <c r="H3">
-        <v>0.01717607973421927</v>
+        <v>-0.2890716803760282</v>
       </c>
       <c r="I3">
-        <v>-0.1093023255813953</v>
+        <v>-0.4465334900117509</v>
       </c>
       <c r="J3">
-        <v>-0.1093023255813953</v>
+        <v>-0.4465334900117509</v>
       </c>
       <c r="K3">
-        <v>-3.38</v>
+        <v>-3.93</v>
       </c>
       <c r="L3">
-        <v>-0.1122923588039867</v>
+        <v>-0.4618096357226792</v>
       </c>
       <c r="M3">
-        <v>1.164</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.2171641791044776</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.3443786982248521</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>0.004</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.0007462686567164179</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>-0.001183431952662722</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>1.16</v>
-      </c>
-      <c r="T3">
-        <v>0.9965635738831615</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>0.308</v>
+        <v>0.221</v>
       </c>
       <c r="V3">
-        <v>0.05746268656716418</v>
+        <v>0.06021798365122616</v>
       </c>
       <c r="W3">
-        <v>-0.2467153284671533</v>
+        <v>-0.5032010243277849</v>
       </c>
       <c r="X3">
-        <v>0.2085586261052945</v>
+        <v>0.1773408300189932</v>
       </c>
       <c r="Y3">
-        <v>-0.4552739545724478</v>
+        <v>-0.6805418543467781</v>
       </c>
       <c r="Z3">
-        <v>1.606018567922314</v>
+        <v>0.7503085875506966</v>
       </c>
       <c r="AA3">
-        <v>-0.175541564400811</v>
+        <v>-0.3350379121847999</v>
       </c>
       <c r="AB3">
-        <v>0.1502201067767823</v>
+        <v>0.1182002844005473</v>
       </c>
       <c r="AC3">
-        <v>-0.3257616711775933</v>
+        <v>-0.4532381965853471</v>
       </c>
       <c r="AD3">
-        <v>3.84</v>
+        <v>3.92</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3.84</v>
+        <v>3.92</v>
       </c>
       <c r="AG3">
-        <v>3.532</v>
+        <v>3.699</v>
       </c>
       <c r="AH3">
-        <v>0.4173913043478261</v>
+        <v>0.5164690382081687</v>
       </c>
       <c r="AI3">
-        <v>0.3296137339055794</v>
+        <v>0.2796005706134094</v>
       </c>
       <c r="AJ3">
-        <v>0.3972109761583446</v>
+        <v>0.5019677025376578</v>
       </c>
       <c r="AK3">
-        <v>0.3114089225886087</v>
+        <v>0.2680629031089209</v>
       </c>
       <c r="AL3">
-        <v>0.355</v>
+        <v>0.136</v>
       </c>
       <c r="AM3">
-        <v>0.355</v>
+        <v>0.136</v>
       </c>
       <c r="AN3">
-        <v>-2.219653179190751</v>
+        <v>-1.53125</v>
       </c>
       <c r="AO3">
-        <v>-9.267605633802818</v>
+        <v>-27.94117647058823</v>
       </c>
       <c r="AP3">
-        <v>-2.041618497109827</v>
+        <v>-1.444921875</v>
       </c>
       <c r="AQ3">
-        <v>-9.267605633802818</v>
+        <v>-27.94117647058823</v>
       </c>
     </row>
   </sheetData>
